--- a/src/app/modules/dashboard/excel_files/whole-food-plant-based-stews-1.xlsx
+++ b/src/app/modules/dashboard/excel_files/whole-food-plant-based-stews-1.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'stews', 'soups', 'ethnic', 'variety']</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
